--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/48.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/48.xlsx
@@ -426,13 +426,13 @@
         <v>-4.59279321043499</v>
       </c>
       <c r="E2">
-        <v>-4.743107638445504</v>
+        <v>-7.047190685074174</v>
       </c>
       <c r="F2">
-        <v>-7.590477419637651</v>
+        <v>-7.880332423325604</v>
       </c>
       <c r="G2">
-        <v>-0.3911719010430781</v>
+        <v>-1.247269045861989</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.985392974068446</v>
       </c>
       <c r="E3">
-        <v>-4.258438650826569</v>
+        <v>-6.845800389005058</v>
       </c>
       <c r="F3">
-        <v>-7.943634732471634</v>
+        <v>-7.524815784604095</v>
       </c>
       <c r="G3">
-        <v>0.04563803013605867</v>
+        <v>-0.672945674072606</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.471555608607393</v>
       </c>
       <c r="E4">
-        <v>-4.990131367089914</v>
+        <v>-8.149385030749077</v>
       </c>
       <c r="F4">
-        <v>-8.167238566599009</v>
+        <v>-8.006055709275723</v>
       </c>
       <c r="G4">
-        <v>-0.01464369358853037</v>
+        <v>-0.06204408461981523</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.136267867569628</v>
       </c>
       <c r="E5">
-        <v>-5.633577710365787</v>
+        <v>-7.115443845317781</v>
       </c>
       <c r="F5">
-        <v>-8.093887247493036</v>
+        <v>-7.898038651386695</v>
       </c>
       <c r="G5">
-        <v>-0.06383840030210021</v>
+        <v>-0.7710172751279756</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.952016121557411</v>
       </c>
       <c r="E6">
-        <v>-6.476883725496184</v>
+        <v>-8.618888158916326</v>
       </c>
       <c r="F6">
-        <v>-7.919798374738354</v>
+        <v>-8.299483553508907</v>
       </c>
       <c r="G6">
-        <v>0.07019565694637234</v>
+        <v>-1.407482897235018</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.907939113080516</v>
       </c>
       <c r="E7">
-        <v>-7.557545177264616</v>
+        <v>-9.367757377090765</v>
       </c>
       <c r="F7">
-        <v>-8.077614273285416</v>
+        <v>-7.609777251776154</v>
       </c>
       <c r="G7">
-        <v>-0.2072081959713175</v>
+        <v>-0.9030749366895032</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.959482468858014</v>
       </c>
       <c r="E8">
-        <v>-8.050474101473542</v>
+        <v>-9.974740447656876</v>
       </c>
       <c r="F8">
-        <v>-8.110524869987685</v>
+        <v>-7.730553040446439</v>
       </c>
       <c r="G8">
-        <v>0.6340378415584231</v>
+        <v>-1.269870140258594</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.067720427662891</v>
       </c>
       <c r="E9">
-        <v>-9.318365311089103</v>
+        <v>-10.85339573089115</v>
       </c>
       <c r="F9">
-        <v>-8.001151763908563</v>
+        <v>-7.95486281148562</v>
       </c>
       <c r="G9">
-        <v>-0.3254608826340843</v>
+        <v>-1.943983286238228</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.1790810632192</v>
       </c>
       <c r="E10">
-        <v>-10.42738859556757</v>
+        <v>-11.23804431310267</v>
       </c>
       <c r="F10">
-        <v>-8.045748130634381</v>
+        <v>-7.769743822956382</v>
       </c>
       <c r="G10">
-        <v>-0.7779065203951989</v>
+        <v>-1.469254366452279</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.248277745032914</v>
       </c>
       <c r="E11">
-        <v>-10.65964497047297</v>
+        <v>-12.73801075866332</v>
       </c>
       <c r="F11">
-        <v>-7.401196056036158</v>
+        <v>-7.584941971536711</v>
       </c>
       <c r="G11">
-        <v>-0.04780542825540986</v>
+        <v>-1.960526082297966</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.238306418674653</v>
       </c>
       <c r="E12">
-        <v>-10.86427312545757</v>
+        <v>-13.48453875577579</v>
       </c>
       <c r="F12">
-        <v>-7.512536124862256</v>
+        <v>-7.47357893897484</v>
       </c>
       <c r="G12">
-        <v>-0.02611804442764431</v>
+        <v>-1.758811232044634</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.12176632088747</v>
       </c>
       <c r="E13">
-        <v>-12.11766868977458</v>
+        <v>-14.2986225281347</v>
       </c>
       <c r="F13">
-        <v>-7.2665343338993</v>
+        <v>-7.272633185379657</v>
       </c>
       <c r="G13">
-        <v>-0.29908907686825</v>
+        <v>-1.72985057966709</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.890411801766003</v>
       </c>
       <c r="E14">
-        <v>-12.69028064262247</v>
+        <v>-15.7621347579336</v>
       </c>
       <c r="F14">
-        <v>-7.136493073770737</v>
+        <v>-7.091332511812544</v>
       </c>
       <c r="G14">
-        <v>0.3687009271313768</v>
+        <v>-1.515237843992756</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.550525630071012</v>
       </c>
       <c r="E15">
-        <v>-13.65690606192975</v>
+        <v>-15.03862952267612</v>
       </c>
       <c r="F15">
-        <v>-7.172292745989245</v>
+        <v>-6.730391680330655</v>
       </c>
       <c r="G15">
-        <v>0.6233811954675091</v>
+        <v>-1.520104345935485</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.124482018425822</v>
       </c>
       <c r="E16">
-        <v>-13.82166100327681</v>
+        <v>-15.14705930431578</v>
       </c>
       <c r="F16">
-        <v>-6.487136827278029</v>
+        <v>-6.649126978691711</v>
       </c>
       <c r="G16">
-        <v>0.5124282617188353</v>
+        <v>-0.4721246711148764</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.652366076451548</v>
       </c>
       <c r="E17">
-        <v>-15.35651934106657</v>
+        <v>-16.89657183854312</v>
       </c>
       <c r="F17">
-        <v>-6.367714711238966</v>
+        <v>-6.38397184838743</v>
       </c>
       <c r="G17">
-        <v>0.9061646848865147</v>
+        <v>0.3495692844599285</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.1821967250612</v>
       </c>
       <c r="E18">
-        <v>-15.25213801518976</v>
+        <v>-16.84245657415146</v>
       </c>
       <c r="F18">
-        <v>-6.249299436235643</v>
+        <v>-6.2288466661907</v>
       </c>
       <c r="G18">
-        <v>0.4534508929367191</v>
+        <v>0.1122362747495771</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.7655925632840856</v>
       </c>
       <c r="E19">
-        <v>-17.24972488403129</v>
+        <v>-18.84930870081267</v>
       </c>
       <c r="F19">
-        <v>-5.788018165363341</v>
+        <v>-5.906387512895116</v>
       </c>
       <c r="G19">
-        <v>0.7899943313679495</v>
+        <v>0.9995055163662658</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.4499632596677046</v>
       </c>
       <c r="E20">
-        <v>-17.95432374030674</v>
+        <v>-20.26394058217279</v>
       </c>
       <c r="F20">
-        <v>-5.733191850276743</v>
+        <v>-5.464344309630615</v>
       </c>
       <c r="G20">
-        <v>1.23882485340018</v>
+        <v>0.003153799230591528</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.2652287961709488</v>
       </c>
       <c r="E21">
-        <v>-18.28639673928921</v>
+        <v>-20.86719671863059</v>
       </c>
       <c r="F21">
-        <v>-5.179517968150662</v>
+        <v>-5.558576395305178</v>
       </c>
       <c r="G21">
-        <v>1.166002783172832</v>
+        <v>0.185064966068004</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.229670535611784</v>
       </c>
       <c r="E22">
-        <v>-19.23175644465647</v>
+        <v>-21.89428179441427</v>
       </c>
       <c r="F22">
-        <v>-4.968116984028227</v>
+        <v>-4.839907279790869</v>
       </c>
       <c r="G22">
-        <v>1.110349202112144</v>
+        <v>-0.208813810557864</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.3431107992617674</v>
       </c>
       <c r="E23">
-        <v>-19.60540536350335</v>
+        <v>-23.08880266815756</v>
       </c>
       <c r="F23">
-        <v>-4.499492068826033</v>
+        <v>-4.975110629350808</v>
       </c>
       <c r="G23">
-        <v>0.5538498075061964</v>
+        <v>-0.586480845677921</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.5896402067538515</v>
       </c>
       <c r="E24">
-        <v>-19.65466157528479</v>
+        <v>-21.76292887734778</v>
       </c>
       <c r="F24">
-        <v>-4.381295345239041</v>
+        <v>-4.94273097005669</v>
       </c>
       <c r="G24">
-        <v>0.00884793755813797</v>
+        <v>0.4232653387096444</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.94500688046995</v>
       </c>
       <c r="E25">
-        <v>-20.39375381807666</v>
+        <v>-23.080212152965</v>
       </c>
       <c r="F25">
-        <v>-4.21935349685578</v>
+        <v>-4.047018578402447</v>
       </c>
       <c r="G25">
-        <v>-0.2249229251519576</v>
+        <v>-0.7135627572939242</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.370422518288067</v>
       </c>
       <c r="E26">
-        <v>-20.13983322351857</v>
+        <v>-22.96653386995046</v>
       </c>
       <c r="F26">
-        <v>-4.233861034894163</v>
+        <v>-4.903245222319996</v>
       </c>
       <c r="G26">
-        <v>-0.8682049605243598</v>
+        <v>-1.067605739445742</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.824955146417168</v>
       </c>
       <c r="E27">
-        <v>-20.36753395357226</v>
+        <v>-23.56590910418368</v>
       </c>
       <c r="F27">
-        <v>-3.883842231258102</v>
+        <v>-4.23157337169931</v>
       </c>
       <c r="G27">
-        <v>-0.9338729418413431</v>
+        <v>-0.910775265613848</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.265257409250392</v>
       </c>
       <c r="E28">
-        <v>-20.6997111074569</v>
+        <v>-23.78923532834595</v>
       </c>
       <c r="F28">
-        <v>-4.087296970949819</v>
+        <v>-4.292698877064569</v>
       </c>
       <c r="G28">
-        <v>-1.625763717366864</v>
+        <v>-2.487422578691751</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.650560763191689</v>
       </c>
       <c r="E29">
-        <v>-21.04465402956916</v>
+        <v>-23.11813812277925</v>
       </c>
       <c r="F29">
-        <v>-4.034256284282879</v>
+        <v>-4.238601066699073</v>
       </c>
       <c r="G29">
-        <v>-1.048848188420231</v>
+        <v>-1.593426308539263</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.950551994534661</v>
       </c>
       <c r="E30">
-        <v>-20.91996249776796</v>
+        <v>-22.74490129506705</v>
       </c>
       <c r="F30">
-        <v>-4.046963940548365</v>
+        <v>-4.804081476424756</v>
       </c>
       <c r="G30">
-        <v>-1.887823191710032</v>
+        <v>-1.142864371189994</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.144202227787696</v>
       </c>
       <c r="E31">
-        <v>-21.37815802633806</v>
+        <v>-22.66476089055331</v>
       </c>
       <c r="F31">
-        <v>-4.326887128514119</v>
+        <v>-4.360388843449324</v>
       </c>
       <c r="G31">
-        <v>-1.546151718238471</v>
+        <v>-1.60375190007625</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.223821279136634</v>
       </c>
       <c r="E32">
-        <v>-20.12829467174703</v>
+        <v>-21.91973634681138</v>
       </c>
       <c r="F32">
-        <v>-4.080863165668347</v>
+        <v>-4.484379555127952</v>
       </c>
       <c r="G32">
-        <v>-1.797144038843855</v>
+        <v>-1.58508042323476</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.193524768562642</v>
       </c>
       <c r="E33">
-        <v>-19.83115432125973</v>
+        <v>-23.15021330417557</v>
       </c>
       <c r="F33">
-        <v>-4.202560671181417</v>
+        <v>-4.492418446354723</v>
       </c>
       <c r="G33">
-        <v>-1.303432450935725</v>
+        <v>-1.108461181945888</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.065783363636299</v>
       </c>
       <c r="E34">
-        <v>-20.74509547396177</v>
+        <v>-22.38726506031129</v>
       </c>
       <c r="F34">
-        <v>-4.319357398739162</v>
+        <v>-4.579660845971493</v>
       </c>
       <c r="G34">
-        <v>-1.012266660211285</v>
+        <v>-1.637959767133539</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.85939899272755</v>
       </c>
       <c r="E35">
-        <v>-19.9187485939901</v>
+        <v>-21.68473571665734</v>
       </c>
       <c r="F35">
-        <v>-4.257918319602646</v>
+        <v>-4.737329063941941</v>
       </c>
       <c r="G35">
-        <v>-0.519607825784643</v>
+        <v>-1.06952254531298</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.593896463259911</v>
       </c>
       <c r="E36">
-        <v>-18.98390853374266</v>
+        <v>-22.16604910503659</v>
       </c>
       <c r="F36">
-        <v>-4.048706017055348</v>
+        <v>-4.268198154699763</v>
       </c>
       <c r="G36">
-        <v>-0.3519949051313429</v>
+        <v>-1.57013662067049</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.287156071726232</v>
       </c>
       <c r="E37">
-        <v>-19.60948099011026</v>
+        <v>-21.41251555863425</v>
       </c>
       <c r="F37">
-        <v>-4.572737675562149</v>
+        <v>-4.588276206151484</v>
       </c>
       <c r="G37">
-        <v>0.287218469773295</v>
+        <v>-0.8747697723287345</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.952548791045897</v>
       </c>
       <c r="E38">
-        <v>-18.60098530012806</v>
+        <v>-21.43581002892971</v>
       </c>
       <c r="F38">
-        <v>-4.316272339615885</v>
+        <v>-4.444034646932132</v>
       </c>
       <c r="G38">
-        <v>0.5115906936973997</v>
+        <v>-0.7743211995761682</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.59898988575217</v>
       </c>
       <c r="E39">
-        <v>-18.38582844307563</v>
+        <v>-21.36397031727202</v>
       </c>
       <c r="F39">
-        <v>-4.533894120574166</v>
+        <v>-4.74802145443003</v>
       </c>
       <c r="G39">
-        <v>0.2386428350755689</v>
+        <v>0.3627684295250028</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.234730256084249</v>
       </c>
       <c r="E40">
-        <v>-18.45773608184343</v>
+        <v>-21.23018560966342</v>
       </c>
       <c r="F40">
-        <v>-4.28662853229069</v>
+        <v>-4.104746242726131</v>
       </c>
       <c r="G40">
-        <v>0.7636456994208901</v>
+        <v>-0.3317575402497781</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.865018597334153</v>
       </c>
       <c r="E41">
-        <v>-18.37188527160601</v>
+        <v>-20.06903053240865</v>
       </c>
       <c r="F41">
-        <v>-4.632948590761242</v>
+        <v>-4.771499102773462</v>
       </c>
       <c r="G41">
-        <v>0.8774490128788764</v>
+        <v>-0.1552922208244668</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.4964164255137176</v>
       </c>
       <c r="E42">
-        <v>-18.32536425812522</v>
+        <v>-19.85779080537285</v>
       </c>
       <c r="F42">
-        <v>-4.524201048518719</v>
+        <v>-5.030641693569776</v>
       </c>
       <c r="G42">
-        <v>0.2594330610621919</v>
+        <v>0.06366064005185101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.135767508770147</v>
       </c>
       <c r="E43">
-        <v>-18.17778129021524</v>
+        <v>-19.13139187522447</v>
       </c>
       <c r="F43">
-        <v>-4.328572983461104</v>
+        <v>-4.35262234964001</v>
       </c>
       <c r="G43">
-        <v>0.8166442229590825</v>
+        <v>0.1377738230395151</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.2121045733661225</v>
       </c>
       <c r="E44">
-        <v>-17.02281663692895</v>
+        <v>-17.92855219472909</v>
       </c>
       <c r="F44">
-        <v>-4.291210193504056</v>
+        <v>-4.665033680755087</v>
       </c>
       <c r="G44">
-        <v>1.934406887201988</v>
+        <v>0.2864140072072521</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.5395495388909398</v>
       </c>
       <c r="E45">
-        <v>-16.85809339489994</v>
+        <v>-17.47291072549932</v>
       </c>
       <c r="F45">
-        <v>-4.567014954236709</v>
+        <v>-4.853154187920562</v>
       </c>
       <c r="G45">
-        <v>2.076955667577467</v>
+        <v>0.4040476218541752</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.8418065133832152</v>
       </c>
       <c r="E46">
-        <v>-16.95963083909993</v>
+        <v>-17.14081961262082</v>
       </c>
       <c r="F46">
-        <v>-4.30588085325173</v>
+        <v>-4.686511900380277</v>
       </c>
       <c r="G46">
-        <v>0.9581667342173865</v>
+        <v>0.3347314193529151</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.113568624071441</v>
       </c>
       <c r="E47">
-        <v>-16.70841827199842</v>
+        <v>-17.55695467460768</v>
       </c>
       <c r="F47">
-        <v>-4.85548857043992</v>
+        <v>-5.074937948024618</v>
       </c>
       <c r="G47">
-        <v>1.813250852101281</v>
+        <v>1.098798708725627</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.348062956194416</v>
       </c>
       <c r="E48">
-        <v>-16.10066988932501</v>
+        <v>-17.7783608257907</v>
       </c>
       <c r="F48">
-        <v>-4.711946217382235</v>
+        <v>-4.746809919404718</v>
       </c>
       <c r="G48">
-        <v>1.758358696514625</v>
+        <v>0.5075385859573318</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.539840152591925</v>
       </c>
       <c r="E49">
-        <v>-15.90139891909149</v>
+        <v>-16.46802875777525</v>
       </c>
       <c r="F49">
-        <v>-4.891369011660116</v>
+        <v>-4.994145982601432</v>
       </c>
       <c r="G49">
-        <v>1.498712609869586</v>
+        <v>0.08530829733314531</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.682403300467632</v>
       </c>
       <c r="E50">
-        <v>-15.62732661519926</v>
+        <v>-15.92783615034827</v>
       </c>
       <c r="F50">
-        <v>-4.949886945235604</v>
+        <v>-4.896414698706706</v>
       </c>
       <c r="G50">
-        <v>1.303817483427152</v>
+        <v>0.8765551655832732</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.77086277357165</v>
       </c>
       <c r="E51">
-        <v>-13.96203011209257</v>
+        <v>-16.46589131804363</v>
       </c>
       <c r="F51">
-        <v>-4.797158306015412</v>
+        <v>-5.059184825283742</v>
       </c>
       <c r="G51">
-        <v>1.492078276608886</v>
+        <v>0.227913356982791</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.801272056292409</v>
       </c>
       <c r="E52">
-        <v>-15.2848652968432</v>
+        <v>-15.41393586300982</v>
       </c>
       <c r="F52">
-        <v>-4.712022235266176</v>
+        <v>-4.541976563713612</v>
       </c>
       <c r="G52">
-        <v>1.729725788145469</v>
+        <v>-0.3484592424954012</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.77054395961495</v>
       </c>
       <c r="E53">
-        <v>-15.3717123713623</v>
+        <v>-15.85889013358149</v>
       </c>
       <c r="F53">
-        <v>-5.136232909922828</v>
+        <v>-5.347707536370331</v>
       </c>
       <c r="G53">
-        <v>2.081696368789703</v>
+        <v>0.1840287653142121</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.677846178180034</v>
       </c>
       <c r="E54">
-        <v>-13.88016435898191</v>
+        <v>-15.61736397238239</v>
       </c>
       <c r="F54">
-        <v>-4.924966540803206</v>
+        <v>-4.975198525029114</v>
       </c>
       <c r="G54">
-        <v>2.108892500394815</v>
+        <v>0.1801322532144899</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.525975107104526</v>
       </c>
       <c r="E55">
-        <v>-14.29481408149424</v>
+        <v>-15.02138056518091</v>
       </c>
       <c r="F55">
-        <v>-5.442433738290511</v>
+        <v>-5.334394904445147</v>
       </c>
       <c r="G55">
-        <v>1.929027250700673</v>
+        <v>0.716046675657249</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.318823356438936</v>
       </c>
       <c r="E56">
-        <v>-13.44119673104838</v>
+        <v>-14.44045433405493</v>
       </c>
       <c r="F56">
-        <v>-5.042502067170503</v>
+        <v>-5.33719648020956</v>
       </c>
       <c r="G56">
-        <v>1.60534859223505</v>
+        <v>0.4932105448633661</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.061498081720393</v>
       </c>
       <c r="E57">
-        <v>-13.32865962348376</v>
+        <v>-13.80881825099106</v>
       </c>
       <c r="F57">
-        <v>-5.435351405436665</v>
+        <v>-5.324834863686597</v>
       </c>
       <c r="G57">
-        <v>1.358057461542571</v>
+        <v>0.4340378538944329</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.7609807900663412</v>
       </c>
       <c r="E58">
-        <v>-13.98233578954297</v>
+        <v>-14.08169503774526</v>
       </c>
       <c r="F58">
-        <v>-5.508605722555317</v>
+        <v>-4.718642917845671</v>
       </c>
       <c r="G58">
-        <v>1.753879528399991</v>
+        <v>-0.5621847519652098</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.4236329085731225</v>
       </c>
       <c r="E59">
-        <v>-13.56734643148005</v>
+        <v>-13.10157929436913</v>
       </c>
       <c r="F59">
-        <v>-5.20328147541183</v>
+        <v>-5.452734161564528</v>
       </c>
       <c r="G59">
-        <v>2.165420065477871</v>
+        <v>-0.2584521303736962</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.05885691027119903</v>
       </c>
       <c r="E60">
-        <v>-12.99155096140477</v>
+        <v>-13.77885786695631</v>
       </c>
       <c r="F60">
-        <v>-5.029588529136009</v>
+        <v>-5.202137247887926</v>
       </c>
       <c r="G60">
-        <v>1.524435548709723</v>
+        <v>-0.08753859581774265</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.3258481023185464</v>
       </c>
       <c r="E61">
-        <v>-13.03701231196777</v>
+        <v>-14.32308534472413</v>
       </c>
       <c r="F61">
-        <v>-5.169604760972969</v>
+        <v>-5.298230979866087</v>
       </c>
       <c r="G61">
-        <v>2.137932605865303</v>
+        <v>-0.0610012627749448</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.724550927353377</v>
       </c>
       <c r="E62">
-        <v>-13.18935470605981</v>
+        <v>-13.67582149785979</v>
       </c>
       <c r="F62">
-        <v>-5.148505047061569</v>
+        <v>-4.945458903496035</v>
       </c>
       <c r="G62">
-        <v>1.800889275057642</v>
+        <v>0.3566836468238223</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.128919283996852</v>
       </c>
       <c r="E63">
-        <v>-12.51430867115841</v>
+        <v>-11.68592397788329</v>
       </c>
       <c r="F63">
-        <v>-5.122520392253996</v>
+        <v>-5.234350618060922</v>
       </c>
       <c r="G63">
-        <v>2.07303267111343</v>
+        <v>-0.314542703445568</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.534236920191402</v>
       </c>
       <c r="E64">
-        <v>-12.59095309373823</v>
+        <v>-14.1527422664516</v>
       </c>
       <c r="F64">
-        <v>-5.207833046212803</v>
+        <v>-5.510448364387931</v>
       </c>
       <c r="G64">
-        <v>0.9211250401784812</v>
+        <v>-1.546820448437403</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.932520677679108</v>
       </c>
       <c r="E65">
-        <v>-13.08083888341401</v>
+        <v>-12.7575420670584</v>
       </c>
       <c r="F65">
-        <v>-5.062146355345614</v>
+        <v>-5.185872588136363</v>
       </c>
       <c r="G65">
-        <v>1.159712746648216</v>
+        <v>-1.968948110149872</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.31501316825108</v>
       </c>
       <c r="E66">
-        <v>-12.71924476237553</v>
+        <v>-12.30935446604526</v>
       </c>
       <c r="F66">
-        <v>-4.931957810566914</v>
+        <v>-5.072448362325547</v>
       </c>
       <c r="G66">
-        <v>0.8016606938483412</v>
+        <v>-1.081192218338911</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.672713344903519</v>
       </c>
       <c r="E67">
-        <v>-11.47584806866746</v>
+        <v>-13.86789672289513</v>
       </c>
       <c r="F67">
-        <v>-5.248242886351156</v>
+        <v>-5.526344020661196</v>
       </c>
       <c r="G67">
-        <v>1.145987224842398</v>
+        <v>-1.690173691378924</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.992893817836011</v>
       </c>
       <c r="E68">
-        <v>-12.54947227182797</v>
+        <v>-13.06511602165937</v>
       </c>
       <c r="F68">
-        <v>-5.375526914480941</v>
+        <v>-5.388661379490637</v>
       </c>
       <c r="G68">
-        <v>0.3034864905532736</v>
+        <v>-1.137150369589212</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.266004083495475</v>
       </c>
       <c r="E69">
-        <v>-12.06103106536065</v>
+        <v>-11.84867280524495</v>
       </c>
       <c r="F69">
-        <v>-5.490795365830285</v>
+        <v>-5.352453902998903</v>
       </c>
       <c r="G69">
-        <v>0.442267870105061</v>
+        <v>-2.131959372503585</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.481326787755416</v>
       </c>
       <c r="E70">
-        <v>-11.9084486621462</v>
+        <v>-11.55915387651257</v>
       </c>
       <c r="F70">
-        <v>-5.309667712134433</v>
+        <v>-5.411758938414364</v>
       </c>
       <c r="G70">
-        <v>0.6505508427083078</v>
+        <v>-1.414309242136996</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.629691766261698</v>
       </c>
       <c r="E71">
-        <v>-12.94280646718621</v>
+        <v>-11.87199897485846</v>
       </c>
       <c r="F71">
-        <v>-5.289922858633692</v>
+        <v>-5.032226983191132</v>
       </c>
       <c r="G71">
-        <v>-0.2116046004474696</v>
+        <v>-1.991804116553001</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.705642344705568</v>
       </c>
       <c r="E72">
-        <v>-12.95117961562639</v>
+        <v>-13.04622322809937</v>
       </c>
       <c r="F72">
-        <v>-4.971324780359949</v>
+        <v>-5.455366280795989</v>
       </c>
       <c r="G72">
-        <v>-0.0503512377751094</v>
+        <v>-2.495480446534337</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.705726186957665</v>
       </c>
       <c r="E73">
-        <v>-12.06852568984334</v>
+        <v>-12.66510685561384</v>
       </c>
       <c r="F73">
-        <v>-5.242696748235288</v>
+        <v>-5.194715210115219</v>
       </c>
       <c r="G73">
-        <v>0.006245848764270816</v>
+        <v>-1.780399299506221</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.6322121625774</v>
       </c>
       <c r="E74">
-        <v>-13.19653233736197</v>
+        <v>-13.17438357099045</v>
       </c>
       <c r="F74">
-        <v>-5.310192710645401</v>
+        <v>-5.332215725105502</v>
       </c>
       <c r="G74">
-        <v>-0.6946794055379213</v>
+        <v>-1.652016343493285</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.489435392885569</v>
       </c>
       <c r="E75">
-        <v>-12.71905909494122</v>
+        <v>-14.37281704627637</v>
       </c>
       <c r="F75">
-        <v>-5.241615868948</v>
+        <v>-5.580142510608675</v>
       </c>
       <c r="G75">
-        <v>-0.8962221074232118</v>
+        <v>-2.474918648189924</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.285394948727218</v>
       </c>
       <c r="E76">
-        <v>-13.61330138570989</v>
+        <v>-13.85646685449977</v>
       </c>
       <c r="F76">
-        <v>-5.544551887571004</v>
+        <v>-5.792165891155877</v>
       </c>
       <c r="G76">
-        <v>-0.4736905591549517</v>
+        <v>-0.8125381372815148</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.030848274008441</v>
       </c>
       <c r="E77">
-        <v>-13.33284393346685</v>
+        <v>-14.43545489875046</v>
       </c>
       <c r="F77">
-        <v>-5.430863974725268</v>
+        <v>-5.767115622838413</v>
       </c>
       <c r="G77">
-        <v>-0.8349405989457629</v>
+        <v>-2.033103172155409</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.736501822722564</v>
       </c>
       <c r="E78">
-        <v>-13.9171167068845</v>
+        <v>-14.19137014973703</v>
       </c>
       <c r="F78">
-        <v>-5.316359661480123</v>
+        <v>-5.366521170792794</v>
       </c>
       <c r="G78">
-        <v>-0.1201772642894173</v>
+        <v>-2.073637491738245</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.416674679808158</v>
       </c>
       <c r="E79">
-        <v>-13.30902868866051</v>
+        <v>-14.61808825547981</v>
       </c>
       <c r="F79">
-        <v>-5.641694032865186</v>
+        <v>-5.468145995680628</v>
       </c>
       <c r="G79">
-        <v>-0.4881708853437239</v>
+        <v>-1.422741201625519</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.083680394180951</v>
       </c>
       <c r="E80">
-        <v>-14.92693471127693</v>
+        <v>-14.64415415186796</v>
       </c>
       <c r="F80">
-        <v>-5.668161717976968</v>
+        <v>-5.549508887086329</v>
       </c>
       <c r="G80">
-        <v>-0.8766965098325904</v>
+        <v>-1.930979463359971</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.750281150303696</v>
       </c>
       <c r="E81">
-        <v>-14.66046118676958</v>
+        <v>-15.39060063644829</v>
       </c>
       <c r="F81">
-        <v>-5.711780938152959</v>
+        <v>-5.655974309104704</v>
       </c>
       <c r="G81">
-        <v>-1.351369150344372</v>
+        <v>-2.285449505886355</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.429754172882668</v>
       </c>
       <c r="E82">
-        <v>-15.71832177190939</v>
+        <v>-17.04765531686102</v>
       </c>
       <c r="F82">
-        <v>-5.720203086211266</v>
+        <v>-6.195618536452386</v>
       </c>
       <c r="G82">
-        <v>-0.1953663745773445</v>
+        <v>-2.983577349207863</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.131154330852648</v>
       </c>
       <c r="E83">
-        <v>-15.00999598152562</v>
+        <v>-16.81395888722119</v>
       </c>
       <c r="F83">
-        <v>-5.540901445435916</v>
+        <v>-6.353589638179161</v>
       </c>
       <c r="G83">
-        <v>-1.378750672499684</v>
+        <v>-2.58045552943635</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.8664713487666893</v>
       </c>
       <c r="E84">
-        <v>-17.1127611876693</v>
+        <v>-17.55267526667043</v>
       </c>
       <c r="F84">
-        <v>-5.743278473252177</v>
+        <v>-6.189071496197959</v>
       </c>
       <c r="G84">
-        <v>-1.126920783872864</v>
+        <v>-3.014812346370887</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.6444705310430315</v>
       </c>
       <c r="E85">
-        <v>-17.68450367350772</v>
+        <v>-18.48460351813094</v>
       </c>
       <c r="F85">
-        <v>-5.890672399096211</v>
+        <v>-6.020551329368442</v>
       </c>
       <c r="G85">
-        <v>-1.435337827402446</v>
+        <v>-2.752848877848357</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4714626095764352</v>
       </c>
       <c r="E86">
-        <v>-19.02133637141606</v>
+        <v>-20.47037559828645</v>
       </c>
       <c r="F86">
-        <v>-5.971095361041099</v>
+        <v>-6.386929815110992</v>
       </c>
       <c r="G86">
-        <v>-1.077020930959429</v>
+        <v>-2.985057163063917</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3544975738887101</v>
       </c>
       <c r="E87">
-        <v>-21.42540359566008</v>
+        <v>-21.34434843939679</v>
       </c>
       <c r="F87">
-        <v>-5.991424602024638</v>
+        <v>-5.89538867531239</v>
       </c>
       <c r="G87">
-        <v>-1.888793181553038</v>
+        <v>-2.836148824707499</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.2941835702284445</v>
       </c>
       <c r="E88">
-        <v>-21.50745954467907</v>
+        <v>-23.03308432396718</v>
       </c>
       <c r="F88">
-        <v>-5.665074283294819</v>
+        <v>-6.332230988350587</v>
       </c>
       <c r="G88">
-        <v>-2.055105057809405</v>
+        <v>-2.666989879287359</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.2908091021472502</v>
       </c>
       <c r="E89">
-        <v>-24.19505452654333</v>
+        <v>-24.95070739878126</v>
       </c>
       <c r="F89">
-        <v>-5.91482470615962</v>
+        <v>-6.266335360768025</v>
       </c>
       <c r="G89">
-        <v>-2.464778447203136</v>
+        <v>-3.131091947892248</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.3432250268164054</v>
       </c>
       <c r="E90">
-        <v>-25.08789751884364</v>
+        <v>-24.71683435865513</v>
       </c>
       <c r="F90">
-        <v>-5.85791185852943</v>
+        <v>-6.243466647349079</v>
       </c>
       <c r="G90">
-        <v>-2.38072700650658</v>
+        <v>-3.155450941970205</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.4459657232975177</v>
       </c>
       <c r="E91">
-        <v>-26.43589743365489</v>
+        <v>-27.21081443432145</v>
       </c>
       <c r="F91">
-        <v>-5.930248418070085</v>
+        <v>-6.371998239813751</v>
       </c>
       <c r="G91">
-        <v>-2.743436996880209</v>
+        <v>-3.12767546489572</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.5964576848396279</v>
       </c>
       <c r="E92">
-        <v>-27.77512116583927</v>
+        <v>-28.99088058267853</v>
       </c>
       <c r="F92">
-        <v>-6.043246626989647</v>
+        <v>-6.084650242589938</v>
       </c>
       <c r="G92">
-        <v>-3.062050520670747</v>
+        <v>-3.928857280309201</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.7901601674938128</v>
       </c>
       <c r="E93">
-        <v>-30.09909327030963</v>
+        <v>-29.63943504463506</v>
       </c>
       <c r="F93">
-        <v>-6.160937356536657</v>
+        <v>-5.761877515523097</v>
       </c>
       <c r="G93">
-        <v>-3.064983664018541</v>
+        <v>-4.133607900822045</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.020934601261806</v>
       </c>
       <c r="E94">
-        <v>-32.73098802187955</v>
+        <v>-32.67797544090875</v>
       </c>
       <c r="F94">
-        <v>-5.920693128429281</v>
+        <v>-5.779280067974904</v>
       </c>
       <c r="G94">
-        <v>-3.675295976365342</v>
+        <v>-4.430179812412115</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.285051802467838</v>
       </c>
       <c r="E95">
-        <v>-34.3121273640277</v>
+        <v>-34.73155689085512</v>
       </c>
       <c r="F95">
-        <v>-5.774633474819004</v>
+        <v>-5.933258251162377</v>
       </c>
       <c r="G95">
-        <v>-3.893619833589198</v>
+        <v>-4.492649806738163</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.579844105562018</v>
       </c>
       <c r="E96">
-        <v>-36.70029511603079</v>
+        <v>-36.70309371296753</v>
       </c>
       <c r="F96">
-        <v>-5.383542841971937</v>
+        <v>-5.820174522123382</v>
       </c>
       <c r="G96">
-        <v>-3.937110470338604</v>
+        <v>-4.64301147458632</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.89591007195662</v>
       </c>
       <c r="E97">
-        <v>-38.62476524354447</v>
+        <v>-39.47102608796487</v>
       </c>
       <c r="F97">
-        <v>-5.648704307099879</v>
+        <v>-5.53475349907218</v>
       </c>
       <c r="G97">
-        <v>-3.843438584304925</v>
+        <v>-5.798219719423923</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.242668578037392</v>
       </c>
       <c r="E98">
-        <v>-41.83953120582666</v>
+        <v>-40.22761182584838</v>
       </c>
       <c r="F98">
-        <v>-5.250545594752206</v>
+        <v>-5.543770328701735</v>
       </c>
       <c r="G98">
-        <v>-4.800000854604099</v>
+        <v>-6.17579074872334</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.600555182590174</v>
       </c>
       <c r="E99">
-        <v>-44.97528661786002</v>
+        <v>-45.04762219742154</v>
       </c>
       <c r="F99">
-        <v>-5.276624480061747</v>
+        <v>-5.375635398336148</v>
       </c>
       <c r="G99">
-        <v>-4.894093179921265</v>
+        <v>-5.910351207384577</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.999447445007575</v>
       </c>
       <c r="E100">
-        <v>-46.13464162669674</v>
+        <v>-46.579944589767</v>
       </c>
       <c r="F100">
-        <v>-5.383395557321801</v>
+        <v>-5.036833191846187</v>
       </c>
       <c r="G100">
-        <v>-5.0123094505831</v>
+        <v>-5.943069328949194</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.396685395621887</v>
       </c>
       <c r="E101">
-        <v>-48.98543488696793</v>
+        <v>-48.43129684383433</v>
       </c>
       <c r="F101">
-        <v>-5.353226751485638</v>
+        <v>-4.87950863805939</v>
       </c>
       <c r="G101">
-        <v>-5.77097724018126</v>
+        <v>-6.808859751107091</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.864716914151169</v>
       </c>
       <c r="E102">
-        <v>-50.65742673889496</v>
+        <v>-51.09539017771729</v>
       </c>
       <c r="F102">
-        <v>-4.817083701990513</v>
+        <v>-4.531946162298175</v>
       </c>
       <c r="G102">
-        <v>-6.218318016720819</v>
+        <v>-7.257412187314022</v>
       </c>
     </row>
   </sheetData>
